--- a/GameConfig/Datas/叙事物品部件配置表.xlsx
+++ b/GameConfig/Datas/叙事物品部件配置表.xlsx
@@ -413,8 +413,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -493,78 +501,79 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>##</t>
+          <t>##group</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>唯一ID</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>部件名称</t>
+          <t>c</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>图片资源</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>关联记忆</t>
+          <t>c</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>图片热点横坐标，归一化0到1</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>图片热点纵坐标，归一化0到1</t>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>##group</t>
+          <t>##</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>唯一ID</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>部件名称</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>图片资源</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>关联记忆</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>图片热点横坐标，归一化0到1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>图片热点纵坐标，归一化0到1</t>
         </is>
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>CAMERA_PART_01</t>
@@ -593,6 +602,7 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>CAMERA_PART_02</t>
@@ -621,6 +631,7 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>GLASS_PART_01</t>
@@ -649,6 +660,7 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>GLASS_PART_02</t>
@@ -677,6 +689,7 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>GLASS_PART_03</t>
@@ -705,6 +718,7 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>CLOCK_PART_01</t>
@@ -733,19 +747,20 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DOLL_SEAM</t>
+          <t>CAMERA_PART_03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>侧边补缀</t>
+          <t>胶片仓</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>scene_chenguo_cat_broken</t>
+          <t>placeholder</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -754,26 +769,27 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="G11" t="n">
-        <v>0.55</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DOLL_NOTE</t>
+          <t>CLOCK_PART_02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>夹层纸条</t>
+          <t>报时鸟</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>scene_chenguo_cat_broken</t>
+          <t>placeholder</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -782,178 +798,329 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.67</v>
+        <v>0.3</v>
       </c>
       <c r="G12" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RADIO_READER</t>
+          <t>CLOCK_PART_03</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>读取模块</t>
+          <t>指针</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>scene_shop_old_radio</t>
+          <t>placeholder</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>M09</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DOLL_PART_01</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>玩偶身体</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>M10</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>RADIO_STORAGE</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>存储模块</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>scene_shop_old_radio</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>DOLL_PART_02</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>右脚</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>M11</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>ZHOU_RADIO_READER</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>可拆卸读取部件</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>scene_zhou_radio</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>DOLL_PART_03</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>腹部</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>DOLL_PART_04</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>缝合痕迹</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>M17</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>RADIO_PART_01</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>磁带仓</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>M13</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>RADIO_PART_02</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>电源线</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>M14</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>RADIO_PART_03</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>电池仓</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>RADIO_PART_04</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>磁带</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>M16</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>ZHOU_RADIO_RECORDING</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>录音存储部分</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>scene_zhou_radio</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>M17</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>RECORDING_NAME</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>录音里的称呼</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>scene_shop_new_radio</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
+      <c r="F21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>TAPE_PART_01</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>时间条</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>M19</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>RECORDING_PAUSE</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>录音里的停顿</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>scene_shop_new_radio</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>M20</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.53</v>
+      <c r="F22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TAPE_PART_02</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>录音内容</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>M18</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>

--- a/GameConfig/Datas/叙事物品部件配置表.xlsx
+++ b/GameConfig/Datas/叙事物品部件配置表.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -573,7 +573,6 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>CAMERA_PART_01</t>
@@ -602,7 +601,6 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>CAMERA_PART_02</t>
@@ -631,7 +629,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>GLASS_PART_01</t>
@@ -660,7 +657,6 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>GLASS_PART_02</t>
@@ -689,7 +685,6 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>GLASS_PART_03</t>
@@ -718,7 +713,6 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>CLOCK_PART_01</t>
@@ -747,7 +741,6 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>CAMERA_PART_03</t>
@@ -776,7 +769,6 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>CLOCK_PART_02</t>
@@ -805,7 +797,6 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>CLOCK_PART_03</t>
@@ -834,7 +825,6 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
           <t>DOLL_PART_01</t>
@@ -856,14 +846,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
           <t>DOLL_PART_02</t>
@@ -885,43 +874,41 @@
         </is>
       </c>
       <c r="F15" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>DOLL_PART_03</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>腹部</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
         <v>0.7</v>
       </c>
-      <c r="G15" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>DOLL_PART_03</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>腹部</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>placeholder</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>0.3</v>
-      </c>
       <c r="G16" t="n">
-        <v>0.7</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
           <t>DOLL_PART_04</t>
@@ -950,7 +937,6 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
           <t>RADIO_PART_01</t>
@@ -979,7 +965,6 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
           <t>RADIO_PART_02</t>
@@ -1008,7 +993,6 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
           <t>RADIO_PART_03</t>
@@ -1037,7 +1021,6 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
           <t>RADIO_PART_04</t>
@@ -1066,7 +1049,6 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
           <t>TAPE_PART_01</t>
@@ -1095,7 +1077,6 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
           <t>TAPE_PART_02</t>

--- a/GameConfig/Datas/叙事物品部件配置表.xlsx
+++ b/GameConfig/Datas/叙事物品部件配置表.xlsx
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.3</v>
+        <v>0.5275</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3</v>
+        <v>0.5574</v>
       </c>
     </row>
     <row r="19">
@@ -986,10 +986,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.7</v>
+        <v>0.211</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3</v>
+        <v>0.394</v>
       </c>
     </row>
     <row r="20">
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.3</v>
+        <v>-1</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="21">
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.7</v>
+        <v>-1</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="22">

--- a/GameConfig/Datas/叙事物品部件配置表.xlsx
+++ b/GameConfig/Datas/叙事物品部件配置表.xlsx
@@ -563,12 +563,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>图片热点横坐标，归一化0到1</t>
+          <t>图片热点横坐标，归一化0到1；(-1,-1)表示这个部件在图上没有位置，改走详情页按钮列表</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>图片热点纵坐标，归一化0到1</t>
+          <t>图片热点纵坐标，归一化0到1（从下往上）；(-1,-1)同上</t>
         </is>
       </c>
     </row>

--- a/GameConfig/Datas/叙事物品部件配置表.xlsx
+++ b/GameConfig/Datas/叙事物品部件配置表.xlsx
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.5275</v>
+        <v>0.615</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5574</v>
+        <v>0.488</v>
       </c>
     </row>
     <row r="19">
@@ -986,10 +986,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.211</v>
+        <v>0.135</v>
       </c>
       <c r="G19" t="n">
-        <v>0.394</v>
+        <v>0.395</v>
       </c>
     </row>
     <row r="20">
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>-1</v>
+        <v>0.235</v>
       </c>
       <c r="G20" t="n">
-        <v>-1</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="21">
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>-1</v>
+        <v>0.47</v>
       </c>
       <c r="G21" t="n">
-        <v>-1</v>
+        <v>0.592</v>
       </c>
     </row>
     <row r="22">
